--- a/AAII_Financials/Yearly/STRO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STRO_YR_FIN.xlsx
@@ -3024,7 +3024,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13500</v>
+        <v>26100</v>
       </c>
       <c r="E59" s="3">
         <v>73800</v>
